--- a/Best ch pipeline/original_best_channels_stat_18m_chair.xlsx
+++ b/Best ch pipeline/original_best_channels_stat_18m_chair.xlsx
@@ -11756,58 +11756,58 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ch_1</t>
+          <t>ch_2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ch_2</t>
+          <t>ch_1</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>56</v>
       </c>
       <c r="I9" t="n">
+        <v>39</v>
+      </c>
+      <c r="J9" t="n">
         <v>43</v>
       </c>
-      <c r="J9" t="n">
-        <v>39</v>
-      </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
         <v>3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>16.0270874605317</v>
       </c>
       <c r="O9" t="n">
+        <v>258.5264717049295</v>
+      </c>
+      <c r="P9" t="n">
         <v>144.7937089851741</v>
-      </c>
-      <c r="P9" t="n">
-        <v>258.5264717049295</v>
       </c>
       <c r="Q9" t="n">
         <v>263.9285714285714</v>
       </c>
       <c r="R9" t="n">
+        <v>348.8974358974359</v>
+      </c>
+      <c r="S9" t="n">
         <v>331.860465116279</v>
-      </c>
-      <c r="S9" t="n">
-        <v>348.8974358974359</v>
       </c>
       <c r="T9" t="n">
         <v>261</v>
       </c>
       <c r="U9" t="n">
+        <v>275</v>
+      </c>
+      <c r="V9" t="n">
         <v>272</v>
-      </c>
-      <c r="V9" t="n">
-        <v>275</v>
       </c>
     </row>
     <row r="10">
@@ -12578,58 +12578,58 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ch_1</t>
+          <t>ch_2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ch_2</t>
+          <t>ch_1</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>101</v>
       </c>
       <c r="I20" t="n">
+        <v>71</v>
+      </c>
+      <c r="J20" t="n">
         <v>79</v>
-      </c>
-      <c r="J20" t="n">
-        <v>71</v>
       </c>
       <c r="K20" t="n">
         <v>5</v>
       </c>
       <c r="L20" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" t="n">
         <v>9</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6</v>
       </c>
       <c r="N20" t="n">
         <v>234.922281650425</v>
       </c>
       <c r="O20" t="n">
+        <v>345.7579496679018</v>
+      </c>
+      <c r="P20" t="n">
         <v>326.2672246028532</v>
-      </c>
-      <c r="P20" t="n">
-        <v>345.7579496679018</v>
       </c>
       <c r="Q20" t="n">
         <v>291.9603960396039</v>
       </c>
       <c r="R20" t="n">
+        <v>387.3098591549296</v>
+      </c>
+      <c r="S20" t="n">
         <v>364.9240506329114</v>
-      </c>
-      <c r="S20" t="n">
-        <v>387.3098591549296</v>
       </c>
       <c r="T20" t="n">
         <v>230</v>
       </c>
       <c r="U20" t="n">
+        <v>240</v>
+      </c>
+      <c r="V20" t="n">
         <v>236</v>
-      </c>
-      <c r="V20" t="n">
-        <v>240</v>
       </c>
     </row>
     <row r="21">
